--- a/xlsx/data.xlsx
+++ b/xlsx/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11013"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10714"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Developer/pokegoldCHS-P/xlsx/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tom/Sync/PokemonCHS/PKMN_G2/pokegoldCHS_build/pokegoldCHS/xlsx/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78CB1B19-C29D-2243-8338-2DB6B17F0A5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24C0634C-03E1-4146-A40B-7D2C4577A37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17240" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
+    <workbookView xWindow="16320" yWindow="5520" windowWidth="29400" windowHeight="17240" xr2:uid="{5D9A02DE-DD85-974B-B8A1-A92382739B9C}"/>
   </bookViews>
   <sheets>
     <sheet name="Misc" sheetId="7" r:id="rId1"/>
@@ -4127,10 +4127,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>"小金@"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>engine/events/specials.asm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -4923,7 +4919,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$69, "008      结束@"</t>
+    <t>$69, "100      结束@"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"阿金@"</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -5451,10 +5451,10 @@
     </row>
     <row r="9" spans="2:8">
       <c r="E9" s="1" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="G9" t="s">
         <v>1</v>
@@ -5465,10 +5465,10 @@
     </row>
     <row r="10" spans="2:8">
       <c r="E10" s="1" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="G10" t="s">
         <v>1</v>
@@ -5482,7 +5482,7 @@
         <v>82</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="G11" t="s">
         <v>1</v>
@@ -5984,7 +5984,7 @@
         <v>82</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="G49" t="s">
         <v>1</v>
@@ -6792,7 +6792,7 @@
     </row>
     <row r="114" spans="2:8">
       <c r="E114" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F114" s="1" t="s">
         <v>627</v>
@@ -6900,7 +6900,7 @@
         <v>216</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G123" t="s">
         <v>1</v>
@@ -7129,7 +7129,7 @@
         <v>578</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G140" t="s">
         <v>1</v>
@@ -7190,7 +7190,7 @@
         <v>198</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="G145" t="s">
         <v>1</v>
@@ -7364,7 +7364,7 @@
         <v>239</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="G160" t="s">
         <v>1</v>
@@ -7378,7 +7378,7 @@
         <v>240</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="G161" t="s">
         <v>1</v>
@@ -7392,7 +7392,7 @@
         <v>241</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="G162" t="s">
         <v>1</v>
@@ -7406,7 +7406,7 @@
         <v>242</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="G163" t="s">
         <v>1</v>
@@ -7470,7 +7470,7 @@
         <v>247</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G168" t="s">
         <v>1</v>
@@ -7481,13 +7481,13 @@
     </row>
     <row r="169" spans="2:8">
       <c r="C169" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>245</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="G169" t="s">
         <v>1</v>
@@ -7876,7 +7876,7 @@
         <v>291</v>
       </c>
       <c r="F209" s="1" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="210" spans="2:8">
@@ -8017,7 +8017,7 @@
         <v>315</v>
       </c>
       <c r="F221" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="G221" t="s">
         <v>1</v>
@@ -8356,7 +8356,7 @@
         <v>367</v>
       </c>
       <c r="F254" s="1" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="G254" t="s">
         <v>1</v>
@@ -8841,7 +8841,7 @@
         <v>436</v>
       </c>
       <c r="F295" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="G295" t="s">
         <v>1</v>
@@ -9021,7 +9021,7 @@
         <v>458</v>
       </c>
       <c r="F310" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="G310" t="s">
         <v>1</v>
@@ -9110,7 +9110,7 @@
         <v>469</v>
       </c>
       <c r="F318" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G318" t="s">
         <v>1</v>
@@ -9367,7 +9367,7 @@
         <v>494</v>
       </c>
       <c r="F337" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G337" t="s">
         <v>1</v>
@@ -10712,7 +10712,7 @@
         <v>653</v>
       </c>
       <c r="F448" s="5" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="449" spans="4:6">
@@ -11037,7 +11037,7 @@
         <v>679</v>
       </c>
       <c r="F479" s="1" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="G479" t="s">
         <v>1</v>
@@ -11140,7 +11140,7 @@
         <v>689</v>
       </c>
       <c r="F487" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="G487" t="s">
         <v>1</v>
@@ -11156,10 +11156,10 @@
     </row>
     <row r="489" spans="2:8">
       <c r="E489" s="1" t="s">
+        <v>995</v>
+      </c>
+      <c r="F489" s="1" t="s">
         <v>996</v>
-      </c>
-      <c r="F489" s="1" t="s">
-        <v>997</v>
       </c>
     </row>
     <row r="490" spans="2:8">
@@ -11486,7 +11486,7 @@
         <v>799</v>
       </c>
       <c r="F519" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="520" spans="2:8">
@@ -11541,7 +11541,7 @@
         <v>799</v>
       </c>
       <c r="F524" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="525" spans="2:8">
@@ -11554,7 +11554,7 @@
         <v>808</v>
       </c>
       <c r="F526" s="1" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="G526" t="s">
         <v>1</v>
@@ -11582,7 +11582,7 @@
         <v>810</v>
       </c>
       <c r="F528" s="1" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="G528" t="s">
         <v>1</v>
@@ -11962,7 +11962,7 @@
     </row>
     <row r="566" spans="2:8">
       <c r="B566" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
     </row>
     <row r="567" spans="2:8">
@@ -11984,7 +11984,7 @@
         <v>862</v>
       </c>
       <c r="F568" s="1" t="s">
-        <v>864</v>
+        <v>1016</v>
       </c>
       <c r="G568" t="s">
         <v>1</v>
@@ -11995,15 +11995,15 @@
     </row>
     <row r="569" spans="2:8">
       <c r="B569" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
     </row>
     <row r="570" spans="2:8">
       <c r="E570" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="F570" s="1" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="G570" t="s">
         <v>1</v>
@@ -12014,10 +12014,10 @@
     </row>
     <row r="571" spans="2:8">
       <c r="E571" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="F571" s="1" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="G571" t="s">
         <v>1</v>
@@ -12028,10 +12028,10 @@
     </row>
     <row r="572" spans="2:8" ht="24">
       <c r="E572" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="F572" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="G572" t="s">
         <v>1</v>
@@ -12042,34 +12042,34 @@
     </row>
     <row r="573" spans="2:8" ht="24">
       <c r="E573" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="F573" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
     </row>
     <row r="574" spans="2:8" ht="24">
       <c r="E574" s="1" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="F574" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="575" spans="2:8" ht="24">
       <c r="E575" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="F575" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
     </row>
     <row r="576" spans="2:8">
       <c r="E576" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="F576" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="G576" t="s">
         <v>1</v>
@@ -12080,7 +12080,7 @@
     </row>
     <row r="577" spans="2:8">
       <c r="B577" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="578" spans="2:8">
@@ -12099,10 +12099,10 @@
     </row>
     <row r="579" spans="2:8">
       <c r="E579" s="1" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="F579" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="G579" t="s">
         <v>1</v>
@@ -12113,10 +12113,10 @@
     </row>
     <row r="580" spans="2:8">
       <c r="E580" s="1" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="F580" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="G580" t="s">
         <v>1</v>
@@ -12127,15 +12127,15 @@
     </row>
     <row r="581" spans="2:8">
       <c r="B581" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
     </row>
     <row r="582" spans="2:8">
       <c r="E582" s="1" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="F582" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="G582" t="s">
         <v>1</v>
@@ -12146,10 +12146,10 @@
     </row>
     <row r="583" spans="2:8">
       <c r="E583" s="1" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="F583" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="G583" t="s">
         <v>1</v>
@@ -12160,10 +12160,10 @@
     </row>
     <row r="584" spans="2:8">
       <c r="E584" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="F584" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="G584" t="s">
         <v>1</v>
@@ -12174,10 +12174,10 @@
     </row>
     <row r="585" spans="2:8">
       <c r="E585" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="F585" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="G585" t="s">
         <v>1</v>
@@ -12188,15 +12188,15 @@
     </row>
     <row r="586" spans="2:8">
       <c r="B586" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
     </row>
     <row r="587" spans="2:8">
       <c r="E587" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="F587" s="1" t="s">
         <v>898</v>
-      </c>
-      <c r="F587" s="1" t="s">
-        <v>899</v>
       </c>
       <c r="G587" t="s">
         <v>1</v>
@@ -12207,7 +12207,7 @@
     </row>
     <row r="589" spans="2:8">
       <c r="B589" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="590" spans="2:8">
@@ -12226,10 +12226,10 @@
     </row>
     <row r="591" spans="2:8">
       <c r="E591" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="F591" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G591" t="s">
         <v>1</v>
@@ -12240,10 +12240,10 @@
     </row>
     <row r="592" spans="2:8">
       <c r="E592" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="F592" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="G592" t="s">
         <v>1</v>
@@ -12254,10 +12254,10 @@
     </row>
     <row r="593" spans="2:8">
       <c r="E593" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="F593" s="1" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="G593" t="s">
         <v>1</v>
@@ -12268,15 +12268,15 @@
     </row>
     <row r="594" spans="2:8">
       <c r="B594" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="595" spans="2:8">
       <c r="E595" s="1" t="s">
+        <v>908</v>
+      </c>
+      <c r="F595" s="1" t="s">
         <v>909</v>
-      </c>
-      <c r="F595" s="1" t="s">
-        <v>910</v>
       </c>
       <c r="G595" t="s">
         <v>1</v>
@@ -12287,7 +12287,7 @@
     </row>
     <row r="596" spans="2:8">
       <c r="E596" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F596" s="1" t="s">
         <v>141</v>
@@ -12301,10 +12301,10 @@
     </row>
     <row r="597" spans="2:8">
       <c r="E597" s="1" t="s">
+        <v>911</v>
+      </c>
+      <c r="F597" s="1" t="s">
         <v>912</v>
-      </c>
-      <c r="F597" s="1" t="s">
-        <v>913</v>
       </c>
       <c r="G597" t="s">
         <v>1</v>
@@ -12315,10 +12315,10 @@
     </row>
     <row r="598" spans="2:8">
       <c r="E598" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="F598" s="1" t="s">
         <v>914</v>
-      </c>
-      <c r="F598" s="1" t="s">
-        <v>915</v>
       </c>
       <c r="G598" t="s">
         <v>1</v>
@@ -12329,10 +12329,10 @@
     </row>
     <row r="599" spans="2:8">
       <c r="E599" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="F599" s="1" t="s">
         <v>916</v>
-      </c>
-      <c r="F599" s="1" t="s">
-        <v>917</v>
       </c>
       <c r="G599" t="s">
         <v>1</v>
@@ -12343,10 +12343,10 @@
     </row>
     <row r="600" spans="2:8">
       <c r="E600" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="F600" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="G600" t="s">
         <v>1</v>
@@ -12357,15 +12357,15 @@
     </row>
     <row r="601" spans="2:8">
       <c r="B601" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="602" spans="2:8">
       <c r="E602" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="F602" s="1" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G602" t="s">
         <v>1</v>
@@ -12376,10 +12376,10 @@
     </row>
     <row r="603" spans="2:8">
       <c r="E603" s="1" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="F603" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G603" t="s">
         <v>1</v>
@@ -12390,10 +12390,10 @@
     </row>
     <row r="604" spans="2:8">
       <c r="E604" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="F604" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G604" t="s">
         <v>1</v>
@@ -12404,10 +12404,10 @@
     </row>
     <row r="605" spans="2:8">
       <c r="E605" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="F605" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="G605" t="s">
         <v>1</v>
@@ -12418,10 +12418,10 @@
     </row>
     <row r="606" spans="2:8">
       <c r="E606" s="1" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="F606" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="G606" t="s">
         <v>1</v>
@@ -12432,10 +12432,10 @@
     </row>
     <row r="607" spans="2:8">
       <c r="E607" s="1" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="F607" s="1" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="G607" t="s">
         <v>1</v>
@@ -12446,10 +12446,10 @@
     </row>
     <row r="608" spans="2:8">
       <c r="E608" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="F608" s="1" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="G608" t="s">
         <v>1</v>
@@ -12460,10 +12460,10 @@
     </row>
     <row r="609" spans="2:8">
       <c r="E609" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="F609" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="G609" t="s">
         <v>1</v>
@@ -12474,10 +12474,10 @@
     </row>
     <row r="610" spans="2:8">
       <c r="E610" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="F610" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="G610" t="s">
         <v>1</v>
@@ -12488,10 +12488,10 @@
     </row>
     <row r="611" spans="2:8">
       <c r="E611" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="F611" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="G611" t="s">
         <v>1</v>
@@ -12502,10 +12502,10 @@
     </row>
     <row r="612" spans="2:8">
       <c r="E612" s="1" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="F612" s="1" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="G612" t="s">
         <v>1</v>
@@ -12516,10 +12516,10 @@
     </row>
     <row r="613" spans="2:8">
       <c r="E613" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="F613" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="G613" t="s">
         <v>1</v>
@@ -12530,10 +12530,10 @@
     </row>
     <row r="614" spans="2:8">
       <c r="E614" s="1" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="F614" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="G614" t="s">
         <v>1</v>
@@ -12544,10 +12544,10 @@
     </row>
     <row r="615" spans="2:8">
       <c r="E615" s="1" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="F615" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="G615" t="s">
         <v>1</v>
@@ -12558,10 +12558,10 @@
     </row>
     <row r="616" spans="2:8">
       <c r="E616" s="1" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="F616" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="G616" t="s">
         <v>1</v>
@@ -12572,10 +12572,10 @@
     </row>
     <row r="617" spans="2:8">
       <c r="E617" s="1" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="F617" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="G617" t="s">
         <v>1</v>
@@ -12586,10 +12586,10 @@
     </row>
     <row r="618" spans="2:8">
       <c r="E618" s="1" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="F618" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="G618" t="s">
         <v>1</v>
@@ -12600,10 +12600,10 @@
     </row>
     <row r="619" spans="2:8">
       <c r="E619" s="1" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="F619" s="1" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="G619" t="s">
         <v>1</v>
@@ -12614,10 +12614,10 @@
     </row>
     <row r="620" spans="2:8">
       <c r="E620" s="1" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
       <c r="F620" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="G620" t="s">
         <v>1</v>
@@ -12628,10 +12628,10 @@
     </row>
     <row r="621" spans="2:8">
       <c r="E621" s="1" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="F621" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="G621" t="s">
         <v>1</v>
@@ -12642,10 +12642,10 @@
     </row>
     <row r="622" spans="2:8">
       <c r="E622" s="1" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
       <c r="F622" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="G622" t="s">
         <v>1</v>
@@ -12656,10 +12656,10 @@
     </row>
     <row r="623" spans="2:8">
       <c r="E623" s="1" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="F623" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G623" t="s">
         <v>1</v>
@@ -12670,7 +12670,7 @@
     </row>
     <row r="624" spans="2:8">
       <c r="B624" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="625" spans="2:8">
@@ -12678,7 +12678,7 @@
         <v>515</v>
       </c>
       <c r="F625" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G625" t="s">
         <v>1</v>
@@ -12689,10 +12689,10 @@
     </row>
     <row r="626" spans="2:8">
       <c r="E626" s="1" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="F626" s="1" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="G626" t="s">
         <v>1</v>
@@ -12706,7 +12706,7 @@
         <v>862</v>
       </c>
       <c r="F627" s="1" t="s">
-        <v>864</v>
+        <v>1016</v>
       </c>
       <c r="G627" t="s">
         <v>1</v>
@@ -12717,10 +12717,10 @@
     </row>
     <row r="628" spans="2:8">
       <c r="E628" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F628" s="1" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="G628" t="s">
         <v>1</v>
@@ -12731,10 +12731,10 @@
     </row>
     <row r="629" spans="2:8">
       <c r="E629" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F629" s="1" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="G629" t="s">
         <v>1</v>
@@ -12745,10 +12745,10 @@
     </row>
     <row r="630" spans="2:8">
       <c r="E630" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F630" s="1" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="G630" t="s">
         <v>1</v>
@@ -12773,10 +12773,10 @@
     </row>
     <row r="632" spans="2:8">
       <c r="E632" s="1" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="F632" s="1" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="G632" t="s">
         <v>1</v>
@@ -12787,10 +12787,10 @@
     </row>
     <row r="633" spans="2:8">
       <c r="E633" s="1" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="F633" s="1" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="G633" t="s">
         <v>1</v>
@@ -12801,10 +12801,10 @@
     </row>
     <row r="634" spans="2:8">
       <c r="E634" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F634" s="1" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="G634" t="s">
         <v>1</v>
@@ -12815,7 +12815,7 @@
     </row>
     <row r="635" spans="2:8">
       <c r="B635" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="636" spans="2:8">
@@ -12834,10 +12834,10 @@
     </row>
     <row r="637" spans="2:8">
       <c r="E637" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="F637" s="1" t="s">
         <v>985</v>
-      </c>
-      <c r="F637" s="1" t="s">
-        <v>986</v>
       </c>
       <c r="G637" t="s">
         <v>1</v>
@@ -12848,7 +12848,7 @@
     </row>
     <row r="638" spans="2:8">
       <c r="B638" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="639" spans="2:8">
@@ -12867,7 +12867,7 @@
     </row>
     <row r="640" spans="2:8">
       <c r="B640" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="641" spans="2:8">
@@ -12886,15 +12886,15 @@
     </row>
     <row r="642" spans="2:8">
       <c r="B642" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="643" spans="2:8">
       <c r="E643" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="F643" s="1" t="s">
         <v>1000</v>
-      </c>
-      <c r="F643" s="1" t="s">
-        <v>1001</v>
       </c>
       <c r="G643" t="s">
         <v>1</v>
@@ -12905,7 +12905,7 @@
     </row>
     <row r="644" spans="2:8">
       <c r="B644" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="645" spans="2:8">
